--- a/hourly datasets/cap_gen_year2final.xlsx
+++ b/hourly datasets/cap_gen_year2final.xlsx
@@ -485,7 +485,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.09866275701177361</v>
+        <v>0.09563041595017861</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.07117535186157629</v>
+        <v>0.06867887098505573</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +503,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.1698381088733499</v>
+        <v>0.1643092869352343</v>
       </c>
     </row>
     <row r="4">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0875375577432094</v>
+        <v>0.08625079916980233</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -521,7 +521,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.186200314754983</v>
+        <v>0.181881215119981</v>
       </c>
     </row>
     <row r="5">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.08929271586081422</v>
+        <v>0.07520683390959083</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
@@ -539,7 +539,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>0.1879554728725878</v>
+        <v>0.1708372498597694</v>
       </c>
     </row>
     <row r="6">
@@ -549,15 +549,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1297238721402159</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+        <v>0.1060564265316105</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.02170495051345114</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3.277458691843679</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.02124264955680107</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.06343663642428704</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.148676216638933</v>
+      </c>
       <c r="H6" t="n">
-        <v>0.2283866291519895</v>
+        <v>0.2016868424817891</v>
       </c>
     </row>
     <row r="7">
@@ -567,25 +577,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01991737152930807</v>
+        <v>0.008536223095035834</v>
       </c>
       <c r="C7" t="n">
-        <v>0.004724198655420279</v>
+        <v>0.002241248111552117</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8523608007022909</v>
+        <v>0.6811837604393002</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02596587967591011</v>
+        <v>0.02523853927691823</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01063935756979954</v>
+        <v>0.004133978880983907</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02919538548881713</v>
+        <v>0.01293846730908771</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1185801285410817</v>
+        <v>0.1041666390452144</v>
       </c>
     </row>
     <row r="8">
@@ -595,25 +605,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01202422563404924</v>
+        <v>0.006687647324011205</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003079965097511697</v>
+        <v>0.001556882413220686</v>
       </c>
       <c r="D8" t="n">
-        <v>0.581425895044372</v>
+        <v>0.6030062260444968</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0247495421370266</v>
+        <v>0.01846194709106787</v>
       </c>
       <c r="F8" t="n">
-        <v>0.005977679743849167</v>
+        <v>0.003634368239251814</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01807077152424898</v>
+        <v>0.009740926408770362</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1106869826458229</v>
+        <v>0.1023180632741898</v>
       </c>
     </row>
     <row r="9">
@@ -623,25 +633,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02075623521033395</v>
+        <v>0.005762110973751945</v>
       </c>
       <c r="C9" t="n">
-        <v>0.005028289645217988</v>
+        <v>0.001727857184516267</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6920075986725491</v>
+        <v>0.4748257744136426</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0119419471126582</v>
+        <v>0.010350310499335</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0108343923415104</v>
+        <v>0.00237048435036531</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0306780780791569</v>
+        <v>0.009153737597138577</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1194189922221076</v>
+        <v>0.1013925269239306</v>
       </c>
     </row>
     <row r="10">
@@ -651,25 +661,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01876962931216891</v>
+        <v>0.004727636144390515</v>
       </c>
       <c r="C10" t="n">
-        <v>0.003990427111981799</v>
+        <v>0.001632461870670689</v>
       </c>
       <c r="D10" t="n">
-        <v>0.563613201886343</v>
+        <v>0.3218310276933745</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01197788420240421</v>
+        <v>0.009891296410763986</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01092969134454767</v>
+        <v>0.001522640536373894</v>
       </c>
       <c r="G10" t="n">
-        <v>0.02660956727978983</v>
+        <v>0.007932631752407096</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1174323863239425</v>
+        <v>0.1003580520945691</v>
       </c>
     </row>
     <row r="11">
@@ -679,7 +689,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02665439086576339</v>
+        <v>0.02733127923017373</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -687,7 +697,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.125317147877537</v>
+        <v>0.1229616951803523</v>
       </c>
     </row>
     <row r="12">
@@ -697,7 +707,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.04444008523698022</v>
+        <v>0.04275985736180826</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -705,7 +715,7 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.1431028422487538</v>
+        <v>0.1383902733119869</v>
       </c>
     </row>
     <row r="13">
@@ -715,7 +725,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.05284586330793421</v>
+        <v>0.05139644933697007</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -723,7 +733,7 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.1515086203197078</v>
+        <v>0.1470268652871487</v>
       </c>
     </row>
     <row r="14">
@@ -733,7 +743,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.05929096156625544</v>
+        <v>0.05783778886395024</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -741,7 +751,7 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.1579537185780291</v>
+        <v>0.1534682048141288</v>
       </c>
     </row>
     <row r="15">
@@ -751,7 +761,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0647307532444439</v>
+        <v>0.06238797785947185</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -759,7 +769,7 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.1633935102562175</v>
+        <v>0.1580183938096505</v>
       </c>
     </row>
     <row r="16">
@@ -769,7 +779,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.06698157313446509</v>
+        <v>0.06418065184213828</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -777,7 +787,7 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.1656443301462387</v>
+        <v>0.1598110677923169</v>
       </c>
     </row>
     <row r="17">
@@ -787,7 +797,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.07122168424452854</v>
+        <v>0.06933002595338843</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -795,7 +805,7 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0.1698844412563021</v>
+        <v>0.164960441903567</v>
       </c>
     </row>
     <row r="18">
@@ -805,22 +815,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.09866275701177361</v>
+        <v>-0.09563041595017861</v>
       </c>
       <c r="C18" t="n">
-        <v>0.01293457410127628</v>
+        <v>0.01167125395904932</v>
       </c>
       <c r="D18" t="n">
-        <v>-15.98674484932656</v>
+        <v>-16.22527021229515</v>
       </c>
       <c r="E18" t="n">
-        <v>0.04324973861679528</v>
+        <v>0.03828551249266934</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.124071371995926</v>
+        <v>-0.1185561622011357</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0732541420276209</v>
+        <v>-0.07270466969922125</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -833,7 +843,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.07367202488660815</v>
+        <v>0.07128702900305574</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -841,7 +851,7 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.1723347818983818</v>
+        <v>0.1669174449532344</v>
       </c>
     </row>
     <row r="20">
@@ -851,7 +861,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.07328462749031499</v>
+        <v>0.07312279779229505</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
@@ -859,7 +869,7 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>0.1719473845020886</v>
+        <v>0.1687532137424737</v>
       </c>
     </row>
     <row r="21">
@@ -869,7 +879,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.0774210796666675</v>
+        <v>0.07611812589501091</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -877,7 +887,7 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>0.1760838366784411</v>
+        <v>0.1717485418451895</v>
       </c>
     </row>
     <row r="22">
@@ -887,25 +897,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.08081373114732876</v>
+        <v>0.07870946275129717</v>
       </c>
       <c r="C22" t="n">
-        <v>0.009102482634710026</v>
+        <v>0.008615561406853841</v>
       </c>
       <c r="D22" t="n">
-        <v>16.21609148284125</v>
+        <v>16.18988814169261</v>
       </c>
       <c r="E22" t="n">
-        <v>0.03801489172310542</v>
+        <v>0.03922218674185272</v>
       </c>
       <c r="F22" t="n">
-        <v>0.06293598043017892</v>
+        <v>0.06178991942942676</v>
       </c>
       <c r="G22" t="n">
-        <v>0.09869148186447806</v>
+        <v>0.09562900607316707</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1794764881591024</v>
+        <v>0.1743398787014758</v>
       </c>
     </row>
     <row r="23">
@@ -915,25 +925,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.08075664033354045</v>
+        <v>0.0786977396961281</v>
       </c>
       <c r="C23" t="n">
-        <v>0.009093407507047017</v>
+        <v>0.0084906052556891</v>
       </c>
       <c r="D23" t="n">
-        <v>15.67383018286934</v>
+        <v>15.67176721023074</v>
       </c>
       <c r="E23" t="n">
-        <v>0.04648444410622087</v>
+        <v>0.04863705394186444</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0628853429116049</v>
+        <v>0.06201493835666003</v>
       </c>
       <c r="G23" t="n">
-        <v>0.09862793775547635</v>
+        <v>0.09538054103559671</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1794193973453141</v>
+        <v>0.1743281556463067</v>
       </c>
     </row>
     <row r="24">
@@ -943,25 +953,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.0765923500713548</v>
+        <v>0.07510812562272874</v>
       </c>
       <c r="C24" t="n">
-        <v>0.009400130650966678</v>
+        <v>0.00886114922171061</v>
       </c>
       <c r="D24" t="n">
-        <v>13.9738056122143</v>
+        <v>14.09040142401086</v>
       </c>
       <c r="E24" t="n">
-        <v>0.04932007785943611</v>
+        <v>0.05272696260553655</v>
       </c>
       <c r="F24" t="n">
-        <v>0.05811731122006756</v>
+        <v>0.05769522649266833</v>
       </c>
       <c r="G24" t="n">
-        <v>0.09506738892264226</v>
+        <v>0.09252102475278925</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1752551070831284</v>
+        <v>0.1707385415729074</v>
       </c>
     </row>
     <row r="25">
@@ -971,25 +981,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.0775071489822161</v>
+        <v>0.0757591672482963</v>
       </c>
       <c r="C25" t="n">
-        <v>0.010352278973985</v>
+        <v>0.009537141691917488</v>
       </c>
       <c r="D25" t="n">
-        <v>12.536241077218</v>
+        <v>12.90769993143099</v>
       </c>
       <c r="E25" t="n">
-        <v>0.06068493445085101</v>
+        <v>0.06123740117868016</v>
       </c>
       <c r="F25" t="n">
-        <v>0.05713154062896972</v>
+        <v>0.05700719837823523</v>
       </c>
       <c r="G25" t="n">
-        <v>0.09788275733546273</v>
+        <v>0.09451113611835747</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1761699059939897</v>
+        <v>0.1713895831984749</v>
       </c>
     </row>
     <row r="26">
@@ -999,25 +1009,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.07571473007823297</v>
+        <v>0.0732778034232867</v>
       </c>
       <c r="C26" t="n">
-        <v>0.009773697408846009</v>
+        <v>0.009289174681914427</v>
       </c>
       <c r="D26" t="n">
-        <v>11.32295039087089</v>
+        <v>11.56291802021018</v>
       </c>
       <c r="E26" t="n">
-        <v>0.07023439580074119</v>
+        <v>0.07017791309040333</v>
       </c>
       <c r="F26" t="n">
-        <v>0.05650815938003449</v>
+        <v>0.05502232349181602</v>
       </c>
       <c r="G26" t="n">
-        <v>0.09492130077643143</v>
+        <v>0.09153328335475744</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1743774870900066</v>
+        <v>0.1689082193734653</v>
       </c>
     </row>
     <row r="27">
@@ -1027,25 +1037,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.07637824796035497</v>
+        <v>0.07305168441429208</v>
       </c>
       <c r="C27" t="n">
-        <v>0.009739343173230108</v>
+        <v>0.009255996098738537</v>
       </c>
       <c r="D27" t="n">
-        <v>10.95541747595428</v>
+        <v>11.06078051496488</v>
       </c>
       <c r="E27" t="n">
-        <v>0.07410456790748245</v>
+        <v>0.07575729133546449</v>
       </c>
       <c r="F27" t="n">
-        <v>0.05723155328387933</v>
+        <v>0.05485220195235184</v>
       </c>
       <c r="G27" t="n">
-        <v>0.09552494263683049</v>
+        <v>0.09125116687623219</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1750410049721286</v>
+        <v>0.1686821003644707</v>
       </c>
     </row>
     <row r="28">
@@ -1055,25 +1065,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.07424768192339194</v>
+        <v>0.07205050104058329</v>
       </c>
       <c r="C28" t="n">
-        <v>0.009322504667293849</v>
+        <v>0.008890799832841944</v>
       </c>
       <c r="D28" t="n">
-        <v>10.50761822850089</v>
+        <v>10.87354603956201</v>
       </c>
       <c r="E28" t="n">
-        <v>0.10448923277448</v>
+        <v>0.1116203223433655</v>
       </c>
       <c r="F28" t="n">
-        <v>0.05592103738459381</v>
+        <v>0.0545693240240511</v>
       </c>
       <c r="G28" t="n">
-        <v>0.09257432646218938</v>
+        <v>0.08953167805711568</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1729104389351656</v>
+        <v>0.1676809169907619</v>
       </c>
     </row>
     <row r="29">
@@ -1083,25 +1093,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0227032714215708</v>
+        <v>0.009931804232376733</v>
       </c>
       <c r="C29" t="n">
-        <v>0.003812182640184231</v>
+        <v>0.002355374638331451</v>
       </c>
       <c r="D29" t="n">
-        <v>1.010503939714208</v>
+        <v>0.5349914617266227</v>
       </c>
       <c r="E29" t="n">
-        <v>0.001264054602835931</v>
+        <v>0.001202831051118984</v>
       </c>
       <c r="F29" t="n">
-        <v>0.01520386516299619</v>
+        <v>0.005307829530298305</v>
       </c>
       <c r="G29" t="n">
-        <v>0.03020267768014518</v>
+        <v>0.01455577893445515</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1213660284333444</v>
+        <v>0.1055622201825553</v>
       </c>
     </row>
   </sheetData>

--- a/hourly datasets/cap_gen_year2final.xlsx
+++ b/hourly datasets/cap_gen_year2final.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,6 +466,11 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>first_seen_iter</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>coef_pos</t>
         </is>
       </c>
@@ -477,7 +482,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>0.2136140478602623</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
@@ -485,7 +490,10 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.09563041595017861</v>
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.0913836636560664</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +503,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.06867887098505573</v>
+        <v>0.3250761627513681</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +511,10 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.1643092869352343</v>
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.2028457785471722</v>
       </c>
     </row>
     <row r="4">
@@ -513,7 +524,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.08625079916980233</v>
+        <v>0.3146851211614711</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -521,7 +532,10 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.181881215119981</v>
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.1924547369572752</v>
       </c>
     </row>
     <row r="5">
@@ -531,7 +545,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.07520683390959083</v>
+        <v>0.3779264878088173</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
@@ -539,7 +553,10 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>0.1708372498597694</v>
+        <v>5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.2556961036046214</v>
       </c>
     </row>
     <row r="6">
@@ -549,25 +566,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1060564265316105</v>
+        <v>0.501529199179449</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02170495051345114</v>
+        <v>0.04917662877159955</v>
       </c>
       <c r="D6" t="n">
-        <v>3.277458691843679</v>
+        <v>5.478698955570979</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02124264955680107</v>
+        <v>0.02188460631976578</v>
       </c>
       <c r="F6" t="n">
-        <v>0.06343663642428704</v>
+        <v>0.1420160869418373</v>
       </c>
       <c r="G6" t="n">
-        <v>0.148676216638933</v>
+        <v>0.3351471329571207</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2016868424817891</v>
+        <v>5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.3792988149752531</v>
       </c>
     </row>
     <row r="7">
@@ -577,25 +597,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.008536223095035834</v>
+        <v>0.3317005404170051</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002241248111552117</v>
+        <v>0.00773328019681178</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6811837604393002</v>
+        <v>1.170786276004947</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02523853927691823</v>
+        <v>0.3316280725135895</v>
       </c>
       <c r="F7" t="n">
-        <v>0.004133978880983907</v>
+        <v>-0.0002162228730492425</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01293846730908771</v>
+        <v>0.03013623926216606</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1041666390452144</v>
+        <v>123</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.2094701562128092</v>
       </c>
     </row>
     <row r="8">
@@ -605,25 +628,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.006687647324011205</v>
+        <v>0.3196959028553482</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001556882413220686</v>
+        <v>0.006723925565979907</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6030062260444968</v>
+        <v>1.336808307057632</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01846194709106787</v>
+        <v>0.592291112093332</v>
       </c>
       <c r="F8" t="n">
-        <v>0.003634368239251814</v>
+        <v>-0.0006064169800684007</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009740926408770362</v>
+        <v>0.02577147298985542</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1023180632741898</v>
+        <v>123</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.1974655186511522</v>
       </c>
     </row>
     <row r="9">
@@ -633,25 +659,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.005762110973751945</v>
+        <v>0.3105229210012957</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001727857184516267</v>
+        <v>0.05122792820974082</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4748257744136426</v>
+        <v>1.611289681975449</v>
       </c>
       <c r="E9" t="n">
-        <v>0.010350310499335</v>
+        <v>0.3392683369802972</v>
       </c>
       <c r="F9" t="n">
-        <v>0.00237048435036531</v>
+        <v>-0.0554757432115691</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009153737597138577</v>
+        <v>0.1453763533995018</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1013925269239306</v>
+        <v>156</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.1882925367970998</v>
       </c>
     </row>
     <row r="10">
@@ -661,25 +690,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.004727636144390515</v>
+        <v>0.3149613922555877</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001632461870670689</v>
+        <v>0.051125582632525</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3218310276933745</v>
+        <v>1.51355205219691</v>
       </c>
       <c r="E10" t="n">
-        <v>0.009891296410763986</v>
+        <v>0.2869962069736807</v>
       </c>
       <c r="F10" t="n">
-        <v>0.001522640536373894</v>
+        <v>-0.05224033084741342</v>
       </c>
       <c r="G10" t="n">
-        <v>0.007932631752407096</v>
+        <v>0.1482111656221683</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1003580520945691</v>
+        <v>156</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.1927310080513918</v>
       </c>
     </row>
     <row r="11">
@@ -689,7 +721,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02733127923017373</v>
+        <v>0.2540729100076302</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -697,7 +729,10 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.1229616951803523</v>
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1318425258034343</v>
       </c>
     </row>
     <row r="12">
@@ -707,7 +742,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.04275985736180826</v>
+        <v>0.2732986018086167</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -715,7 +750,10 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.1383902733119869</v>
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.1510682176044208</v>
       </c>
     </row>
     <row r="13">
@@ -725,7 +763,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.05139644933697007</v>
+        <v>0.2862833464274012</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -733,7 +771,10 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.1470268652871487</v>
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.1640529622232052</v>
       </c>
     </row>
     <row r="14">
@@ -743,7 +784,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.05783778886395024</v>
+        <v>0.2948311782911449</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -751,7 +792,10 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.1534682048141288</v>
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.1726007940869489</v>
       </c>
     </row>
     <row r="15">
@@ -761,7 +805,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.06238797785947185</v>
+        <v>0.2989904822101057</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -769,7 +813,10 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.1580183938096505</v>
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.1767600980059097</v>
       </c>
     </row>
     <row r="16">
@@ -779,7 +826,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.06418065184213828</v>
+        <v>0.3043509853052274</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -787,7 +834,10 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.1598110677923169</v>
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.1821206011010314</v>
       </c>
     </row>
     <row r="17">
@@ -797,7 +847,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.06933002595338843</v>
+        <v>0.3096973488218507</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -805,7 +855,10 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0.164960441903567</v>
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.1874669646176547</v>
       </c>
     </row>
     <row r="18">
@@ -815,24 +868,27 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.09563041595017861</v>
+        <v>0.1222303842041959</v>
       </c>
       <c r="C18" t="n">
-        <v>0.01167125395904932</v>
+        <v>0.01120758575427059</v>
       </c>
       <c r="D18" t="n">
-        <v>-16.22527021229515</v>
+        <v>-16.10771320061728</v>
       </c>
       <c r="E18" t="n">
-        <v>0.03828551249266934</v>
+        <v>0.03694955533288198</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1185561622011357</v>
+        <v>-0.1161842155285987</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.07270466969922125</v>
+        <v>-0.07215282081407198</v>
       </c>
       <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -843,7 +899,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.07128702900305574</v>
+        <v>0.3123838678369738</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -851,7 +907,10 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.1669174449532344</v>
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.1901534836327779</v>
       </c>
     </row>
     <row r="20">
@@ -861,7 +920,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.07312279779229505</v>
+        <v>0.3132884122301033</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
@@ -869,7 +928,10 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>0.1687532137424737</v>
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.1910580280259074</v>
       </c>
     </row>
     <row r="21">
@@ -879,7 +941,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.07611812589501091</v>
+        <v>0.3137718760902569</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -887,7 +949,10 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>0.1717485418451895</v>
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.191541491886061</v>
       </c>
     </row>
     <row r="22">
@@ -897,25 +962,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.07870946275129717</v>
+        <v>0.3151538149183024</v>
       </c>
       <c r="C22" t="n">
-        <v>0.008615561406853841</v>
+        <v>0.008460040827867941</v>
       </c>
       <c r="D22" t="n">
-        <v>16.18988814169261</v>
+        <v>16.10300740219164</v>
       </c>
       <c r="E22" t="n">
-        <v>0.03922218674185272</v>
+        <v>0.03917123292165841</v>
       </c>
       <c r="F22" t="n">
-        <v>0.06178991942942676</v>
+        <v>0.06103439424743063</v>
       </c>
       <c r="G22" t="n">
-        <v>0.09562900607316707</v>
+        <v>0.09426317138305146</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1743398787014758</v>
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.1929234307141064</v>
       </c>
     </row>
     <row r="23">
@@ -925,25 +993,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.0786977396961281</v>
+        <v>0.321088377270226</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0084906052556891</v>
+        <v>0.008432767508395589</v>
       </c>
       <c r="D23" t="n">
-        <v>15.67176721023074</v>
+        <v>15.66085900283388</v>
       </c>
       <c r="E23" t="n">
-        <v>0.04863705394186444</v>
+        <v>0.04851556479586239</v>
       </c>
       <c r="F23" t="n">
-        <v>0.06201493835666003</v>
+        <v>0.06189307997844855</v>
       </c>
       <c r="G23" t="n">
-        <v>0.09538054103559671</v>
+        <v>0.09503124717416954</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1743281556463067</v>
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.1988579930660301</v>
       </c>
     </row>
     <row r="24">
@@ -953,25 +1024,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.07510812562272874</v>
+        <v>0.3198500801910201</v>
       </c>
       <c r="C24" t="n">
-        <v>0.00886114922171061</v>
+        <v>0.008782459662895245</v>
       </c>
       <c r="D24" t="n">
-        <v>14.09040142401086</v>
+        <v>14.06933022252701</v>
       </c>
       <c r="E24" t="n">
-        <v>0.05272696260553655</v>
+        <v>0.05257775961086462</v>
       </c>
       <c r="F24" t="n">
-        <v>0.05769522649266833</v>
+        <v>0.057517333113129</v>
       </c>
       <c r="G24" t="n">
-        <v>0.09252102475278925</v>
+        <v>0.09203372416293902</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1707385415729074</v>
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.1976196959868242</v>
       </c>
     </row>
     <row r="25">
@@ -981,25 +1055,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.0757591672482963</v>
+        <v>0.3244565753790129</v>
       </c>
       <c r="C25" t="n">
-        <v>0.009537141691917488</v>
+        <v>0.00946591762416488</v>
       </c>
       <c r="D25" t="n">
-        <v>12.90769993143099</v>
+        <v>12.87527492320758</v>
       </c>
       <c r="E25" t="n">
-        <v>0.06123740117868016</v>
+        <v>0.06086083152374562</v>
       </c>
       <c r="F25" t="n">
-        <v>0.05700719837823523</v>
+        <v>0.05686844945846824</v>
       </c>
       <c r="G25" t="n">
-        <v>0.09451113611835747</v>
+        <v>0.09409182063769674</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1713895831984749</v>
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.202226191174817</v>
       </c>
     </row>
     <row r="26">
@@ -1009,25 +1086,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0732778034232867</v>
+        <v>0.324512306713747</v>
       </c>
       <c r="C26" t="n">
-        <v>0.009289174681914427</v>
+        <v>0.009175705917500075</v>
       </c>
       <c r="D26" t="n">
-        <v>11.56291802021018</v>
+        <v>11.53478056166548</v>
       </c>
       <c r="E26" t="n">
-        <v>0.07017791309040333</v>
+        <v>0.06963671157100906</v>
       </c>
       <c r="F26" t="n">
-        <v>0.05502232349181602</v>
+        <v>0.0547427952148939</v>
       </c>
       <c r="G26" t="n">
-        <v>0.09153328335475744</v>
+        <v>0.0908075551687457</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1689082193734653</v>
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.2022819225095511</v>
       </c>
     </row>
     <row r="27">
@@ -1037,25 +1117,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.07305168441429208</v>
+        <v>0.3253228354507129</v>
       </c>
       <c r="C27" t="n">
-        <v>0.009255996098738537</v>
+        <v>0.009098849408975523</v>
       </c>
       <c r="D27" t="n">
-        <v>11.06078051496488</v>
+        <v>11.00733086885955</v>
       </c>
       <c r="E27" t="n">
-        <v>0.07575729133546449</v>
+        <v>0.07301449157680948</v>
       </c>
       <c r="F27" t="n">
-        <v>0.05485220195235184</v>
+        <v>0.0543232768816367</v>
       </c>
       <c r="G27" t="n">
-        <v>0.09125116687623219</v>
+        <v>0.09010453411376068</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1686821003644707</v>
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.203092451246517</v>
       </c>
     </row>
     <row r="28">
@@ -1065,25 +1148,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.07205050104058329</v>
+        <v>0.3268284772918839</v>
       </c>
       <c r="C28" t="n">
-        <v>0.008890799832841944</v>
+        <v>0.008696780742988217</v>
       </c>
       <c r="D28" t="n">
-        <v>10.87354603956201</v>
+        <v>10.79004507892104</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1116203223433655</v>
+        <v>0.1046098732867741</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0545693240240511</v>
+        <v>0.05374499559167231</v>
       </c>
       <c r="G28" t="n">
-        <v>0.08953167805711568</v>
+        <v>0.08794472649493937</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1676809169907619</v>
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.2045980930876879</v>
       </c>
     </row>
     <row r="29">
@@ -1093,25 +1179,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.009931804232376733</v>
+        <v>0.3311312433116986</v>
       </c>
       <c r="C29" t="n">
-        <v>0.002355374638331451</v>
+        <v>0.05690678742692037</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5349914617266227</v>
+        <v>4.003226309654699</v>
       </c>
       <c r="E29" t="n">
-        <v>0.001202831051118984</v>
+        <v>0.003556731713887153</v>
       </c>
       <c r="F29" t="n">
-        <v>0.005307829530298305</v>
+        <v>0.08930296024143623</v>
       </c>
       <c r="G29" t="n">
-        <v>0.01455577893445515</v>
+        <v>0.3126924450013278</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1055622201825553</v>
+        <v>138</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.2089008591075026</v>
       </c>
     </row>
   </sheetData>
